--- a/sources/wang_step4.xlsx
+++ b/sources/wang_step4.xlsx
@@ -738,6 +738,11 @@
           <t>Crouch</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>69bbb246-8bd8-4be1-a2c2-f1113edf6288</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>69bbb246-8bd8-4be1-a2c2-f1113edf6288</t>
@@ -780,6 +785,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>b024eb39-fb8b-4f12-9207-4c48609e7fc8</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>b024eb39-fb8b-4f12-9207-4c48609e7fc8</t>
@@ -822,6 +832,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>aeec6651-ae98-4599-8ef6-d5adca58c3cd</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>aeec6651-ae98-4599-8ef6-d5adca58c3cd</t>
@@ -862,6 +877,11 @@
       <c r="L10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0bbb7217-3bd9-4aa5-bd95-cfe77d966840</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -4225,6 +4245,11 @@
       <c r="J81" t="inlineStr">
         <is>
           <t>hmmhlmhhLm</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>f2b1b105-8e73-4505-9cf6-fc48f600c675</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">

--- a/sources/wang_step4.xlsx
+++ b/sources/wang_step4.xlsx
@@ -3428,6 +3428,11 @@
           <t>– d/b+4</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>d+4; d/f+4</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr">
         <is>
           <t>– Low Kick</t>
@@ -3696,6 +3701,11 @@
       <c r="A68" t="inlineStr">
         <is>
           <t>– d/b+4</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>d+4; d/f+4</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
